--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O330"/>
+  <dimension ref="A1:O332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17282,6 +17282,108 @@
         <v>323.03</v>
       </c>
       <c r="O330" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>321.46</v>
+      </c>
+      <c r="C331" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="D331" t="n">
+        <v>336.26</v>
+      </c>
+      <c r="E331" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="F331" t="n">
+        <v>334.14</v>
+      </c>
+      <c r="G331" t="n">
+        <v>344.54</v>
+      </c>
+      <c r="H331" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="I331" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="J331" t="n">
+        <v>332.53</v>
+      </c>
+      <c r="K331" t="n">
+        <v>320.54</v>
+      </c>
+      <c r="L331" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="M331" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="N331" t="n">
+        <v>311.41</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>324.31</v>
+      </c>
+      <c r="C332" t="n">
+        <v>326.56</v>
+      </c>
+      <c r="D332" t="n">
+        <v>338.38</v>
+      </c>
+      <c r="E332" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="F332" t="n">
+        <v>337.62</v>
+      </c>
+      <c r="G332" t="n">
+        <v>346.39</v>
+      </c>
+      <c r="H332" t="n">
+        <v>343.67</v>
+      </c>
+      <c r="I332" t="n">
+        <v>340.58</v>
+      </c>
+      <c r="J332" t="n">
+        <v>335.13</v>
+      </c>
+      <c r="K332" t="n">
+        <v>324.84</v>
+      </c>
+      <c r="L332" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="M332" t="n">
+        <v>331.19</v>
+      </c>
+      <c r="N332" t="n">
+        <v>317.16</v>
+      </c>
+      <c r="O332" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17298,7 +17400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B340"/>
+  <dimension ref="A1:B342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20701,6 +20803,26 @@
       </c>
       <c r="B340" t="n">
         <v>-0.44</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -20869,28 +20991,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07723573844834067</v>
+        <v>0.06501427418844304</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00761843364750725</v>
+        <v>0.005397162033811242</v>
       </c>
       <c r="M2" t="n">
-        <v>5.324026960480483</v>
+        <v>5.354253556979564</v>
       </c>
       <c r="N2" t="n">
-        <v>42.39598400283314</v>
+        <v>42.78763592183384</v>
       </c>
       <c r="O2" t="n">
-        <v>6.511219855206329</v>
+        <v>6.541225873017522</v>
       </c>
       <c r="P2" t="n">
-        <v>331.2152120875757</v>
+        <v>331.3416149191647</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20947,28 +21069,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08404057453389698</v>
+        <v>0.0775968220992809</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01313608067356886</v>
+        <v>0.01129299430925657</v>
       </c>
       <c r="M3" t="n">
-        <v>4.223164673190325</v>
+        <v>4.225087200957576</v>
       </c>
       <c r="N3" t="n">
-        <v>28.94973573717116</v>
+        <v>28.95762838801227</v>
       </c>
       <c r="O3" t="n">
-        <v>5.380495863502839</v>
+        <v>5.381229263654567</v>
       </c>
       <c r="P3" t="n">
-        <v>328.8141115775504</v>
+        <v>328.8807541883247</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21025,28 +21147,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1433256604141059</v>
+        <v>0.1353279570248248</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04330288154931916</v>
+        <v>0.03884555696914782</v>
       </c>
       <c r="M4" t="n">
-        <v>3.956146003507839</v>
+        <v>3.973320872483729</v>
       </c>
       <c r="N4" t="n">
-        <v>24.7617130291483</v>
+        <v>24.89106583662361</v>
       </c>
       <c r="O4" t="n">
-        <v>4.976114250009569</v>
+        <v>4.989094691086111</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3393539627324</v>
+        <v>340.4220701724532</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21103,28 +21225,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1755259710522398</v>
+        <v>0.1672049090199459</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0631688556687543</v>
+        <v>0.05768638384944313</v>
       </c>
       <c r="M5" t="n">
-        <v>4.039138877501309</v>
+        <v>4.050161537912577</v>
       </c>
       <c r="N5" t="n">
-        <v>24.9296506950067</v>
+        <v>25.08631181999239</v>
       </c>
       <c r="O5" t="n">
-        <v>4.992960113500477</v>
+        <v>5.008623745101282</v>
       </c>
       <c r="P5" t="n">
-        <v>336.6554842891659</v>
+        <v>336.7415406238192</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21181,28 +21303,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04203155419306395</v>
+        <v>0.02984120280345209</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003579784516092976</v>
+        <v>0.001787402194285304</v>
       </c>
       <c r="M6" t="n">
-        <v>4.238801680826181</v>
+        <v>4.27719641663653</v>
       </c>
       <c r="N6" t="n">
-        <v>26.82944303874234</v>
+        <v>27.31807074879112</v>
       </c>
       <c r="O6" t="n">
-        <v>5.179714571165321</v>
+        <v>5.226669183025756</v>
       </c>
       <c r="P6" t="n">
-        <v>345.1050433738754</v>
+        <v>345.2311204562924</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21259,28 +21381,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08388762727464513</v>
+        <v>0.07734901089118723</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01573273864945524</v>
+        <v>0.01347402607793591</v>
       </c>
       <c r="M7" t="n">
-        <v>3.893039277961316</v>
+        <v>3.901163338752208</v>
       </c>
       <c r="N7" t="n">
-        <v>24.020367475405</v>
+        <v>24.06230829691897</v>
       </c>
       <c r="O7" t="n">
-        <v>4.901057791477775</v>
+        <v>4.905334677360861</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8087074513075</v>
+        <v>348.8763323690627</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21337,28 +21459,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08686435741826387</v>
+        <v>0.07517741727233697</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K8" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0122513301124898</v>
+        <v>0.009160782117588862</v>
       </c>
       <c r="M8" t="n">
-        <v>4.66974911934514</v>
+        <v>4.69288096550608</v>
       </c>
       <c r="N8" t="n">
-        <v>33.19109253578789</v>
+        <v>33.57855894665263</v>
       </c>
       <c r="O8" t="n">
-        <v>5.761171108011625</v>
+        <v>5.794700936774273</v>
       </c>
       <c r="P8" t="n">
-        <v>350.2274770086478</v>
+        <v>350.3483550393983</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21415,28 +21537,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1028215336913505</v>
+        <v>0.0872096204773796</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K9" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01325405585726203</v>
+        <v>0.00945754276824573</v>
       </c>
       <c r="M9" t="n">
-        <v>5.30014955635064</v>
+        <v>5.33639043576191</v>
       </c>
       <c r="N9" t="n">
-        <v>42.94373583380381</v>
+        <v>43.75625974414547</v>
       </c>
       <c r="O9" t="n">
-        <v>6.553147017563684</v>
+        <v>6.614851452916041</v>
       </c>
       <c r="P9" t="n">
-        <v>348.7179664656587</v>
+        <v>348.879428543952</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21493,28 +21615,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1423934746566711</v>
+        <v>0.1310601647374583</v>
       </c>
       <c r="J10" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K10" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02354525398746843</v>
+        <v>0.02003215046597029</v>
       </c>
       <c r="M10" t="n">
-        <v>5.449063950770547</v>
+        <v>5.475197989568082</v>
       </c>
       <c r="N10" t="n">
-        <v>45.87795282958181</v>
+        <v>46.15750128518744</v>
       </c>
       <c r="O10" t="n">
-        <v>6.77332657042179</v>
+        <v>6.793931209924593</v>
       </c>
       <c r="P10" t="n">
-        <v>339.703410710421</v>
+        <v>339.8206278885301</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21571,28 +21693,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1421226524830196</v>
+        <v>0.1230184908359769</v>
       </c>
       <c r="J11" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K11" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01784143733079202</v>
+        <v>0.0132556572834005</v>
       </c>
       <c r="M11" t="n">
-        <v>6.397173847617735</v>
+        <v>6.44814051486792</v>
       </c>
       <c r="N11" t="n">
-        <v>60.66713572657457</v>
+        <v>61.88149325997485</v>
       </c>
       <c r="O11" t="n">
-        <v>7.788911074506793</v>
+        <v>7.866479089146227</v>
       </c>
       <c r="P11" t="n">
-        <v>335.1505841590948</v>
+        <v>335.3481735302307</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21649,28 +21771,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1591854771739299</v>
+        <v>0.1424376895847803</v>
       </c>
       <c r="J12" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K12" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01858610480792577</v>
+        <v>0.01488143145300314</v>
       </c>
       <c r="M12" t="n">
-        <v>6.922198375443924</v>
+        <v>6.954843494577028</v>
       </c>
       <c r="N12" t="n">
-        <v>73.00385974591403</v>
+        <v>73.77517619891216</v>
       </c>
       <c r="O12" t="n">
-        <v>8.544229616876763</v>
+        <v>8.5892477085547</v>
       </c>
       <c r="P12" t="n">
-        <v>334.3384355357936</v>
+        <v>334.5116549484135</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21727,28 +21849,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2017005144049672</v>
+        <v>0.1858559114889652</v>
       </c>
       <c r="J13" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K13" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03600658563904391</v>
+        <v>0.03058150340353627</v>
       </c>
       <c r="M13" t="n">
-        <v>6.280964153963675</v>
+        <v>6.329694259215037</v>
       </c>
       <c r="N13" t="n">
-        <v>59.42665039653587</v>
+        <v>60.14809067742504</v>
       </c>
       <c r="O13" t="n">
-        <v>7.708868295446218</v>
+        <v>7.755520013346947</v>
       </c>
       <c r="P13" t="n">
-        <v>337.8932729326283</v>
+        <v>338.0571538812664</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21805,28 +21927,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2039955829397063</v>
+        <v>0.1734376012852304</v>
       </c>
       <c r="J14" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K14" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03699487442443272</v>
+        <v>0.02564960221954926</v>
       </c>
       <c r="M14" t="n">
-        <v>6.367183747838486</v>
+        <v>6.509994147966034</v>
       </c>
       <c r="N14" t="n">
-        <v>59.10220487053082</v>
+        <v>62.76790978930122</v>
       </c>
       <c r="O14" t="n">
-        <v>7.687795839545352</v>
+        <v>7.922620134103441</v>
       </c>
       <c r="P14" t="n">
-        <v>334.8260872896946</v>
+        <v>335.1421475571463</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -21864,7 +21986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O330"/>
+  <dimension ref="A1:O332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47277,6 +47399,160 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-36.69364544518393,175.60401036820892</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-36.69436346987422,175.60417335095718</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-36.69507503345779,175.60448907583273</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-36.69577212498936,175.60484057748192</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-36.696417252537266,175.60527190699037</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-36.696997811674905,175.60583566394143</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-36.697617421439546,175.6063190817061</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-36.698233215813254,175.60683577905095</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>-36.698762463791866,175.60747736675617</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>-36.6993403299805,175.60804328012836</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>-36.69981738873374,175.60873716856378</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-36.70025438849507,175.60951581191873</t>
+        </is>
+      </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>-36.70072532245695,175.6102758553164</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>-36.69364137030968,175.60404184639853</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>-36.694360072058316,175.60419543715528</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>-36.69506880694695,175.60451149645039</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>-36.695760365382135,175.60486942233248</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>-36.69640162435918,175.60530565631416</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>-36.696988646724044,175.60585295012748</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>-36.69760582360562,175.6063382059955</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>-36.698203691310795,175.60687486074954</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>-36.698745191242956,175.60749701352847</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>-36.699311434309145,175.60807532057737</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>-36.69979273339155,175.60876246469152</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>-36.700232372863525,175.6095326487399</t>
+        </is>
+      </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>-36.70067844551564,175.61030322937927</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O332"/>
+  <dimension ref="A1:O334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17384,6 +17384,108 @@
         <v>317.16</v>
       </c>
       <c r="O332" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>323.93</v>
+      </c>
+      <c r="C333" t="n">
+        <v>327.62</v>
+      </c>
+      <c r="D333" t="n">
+        <v>338.39</v>
+      </c>
+      <c r="E333" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="F333" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="G333" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="H333" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="I333" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="J333" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="K333" t="n">
+        <v>326.77</v>
+      </c>
+      <c r="L333" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="M333" t="n">
+        <v>332.03</v>
+      </c>
+      <c r="N333" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>325.57</v>
+      </c>
+      <c r="C334" t="n">
+        <v>329.16</v>
+      </c>
+      <c r="D334" t="n">
+        <v>341.06</v>
+      </c>
+      <c r="E334" t="n">
+        <v>337.56</v>
+      </c>
+      <c r="F334" t="n">
+        <v>341.19</v>
+      </c>
+      <c r="G334" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="H334" t="n">
+        <v>345.08</v>
+      </c>
+      <c r="I334" t="n">
+        <v>343.58</v>
+      </c>
+      <c r="J334" t="n">
+        <v>337.81</v>
+      </c>
+      <c r="K334" t="n">
+        <v>330.35</v>
+      </c>
+      <c r="L334" t="n">
+        <v>330.87</v>
+      </c>
+      <c r="M334" t="n">
+        <v>334.85</v>
+      </c>
+      <c r="N334" t="n">
+        <v>324.38</v>
+      </c>
+      <c r="O334" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17400,7 +17502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B342"/>
+  <dimension ref="A1:B344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20823,6 +20925,26 @@
       </c>
       <c r="B342" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -20991,28 +21113,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06501427418844304</v>
+        <v>0.05530324827680271</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005397162033811242</v>
+        <v>0.003923348125748127</v>
       </c>
       <c r="M2" t="n">
-        <v>5.354253556979564</v>
+        <v>5.371770330185006</v>
       </c>
       <c r="N2" t="n">
-        <v>42.78763592183384</v>
+        <v>42.9412333105921</v>
       </c>
       <c r="O2" t="n">
-        <v>6.541225873017522</v>
+        <v>6.552956074215063</v>
       </c>
       <c r="P2" t="n">
-        <v>331.3416149191647</v>
+        <v>331.4425141359429</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21069,28 +21191,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0775968220992809</v>
+        <v>0.07463484646708911</v>
       </c>
       <c r="J3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K3" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01129299430925657</v>
+        <v>0.01057385099178598</v>
       </c>
       <c r="M3" t="n">
-        <v>4.225087200957576</v>
+        <v>4.212109532743692</v>
       </c>
       <c r="N3" t="n">
-        <v>28.95762838801227</v>
+        <v>28.82509869764321</v>
       </c>
       <c r="O3" t="n">
-        <v>5.381229263654567</v>
+        <v>5.368901069832002</v>
       </c>
       <c r="P3" t="n">
-        <v>328.8807541883247</v>
+        <v>328.9115264512066</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21147,28 +21269,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1353279570248248</v>
+        <v>0.1303560273247323</v>
       </c>
       <c r="J4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K4" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03884555696914782</v>
+        <v>0.03642528616902241</v>
       </c>
       <c r="M4" t="n">
-        <v>3.973320872483729</v>
+        <v>3.974626030012717</v>
       </c>
       <c r="N4" t="n">
-        <v>24.89106583662361</v>
+        <v>24.858903763918</v>
       </c>
       <c r="O4" t="n">
-        <v>4.989094691086111</v>
+        <v>4.985870411865715</v>
       </c>
       <c r="P4" t="n">
-        <v>340.4220701724532</v>
+        <v>340.4737237759194</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21225,28 +21347,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1672049090199459</v>
+        <v>0.1621458537228388</v>
       </c>
       <c r="J5" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K5" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05768638384944313</v>
+        <v>0.05485916296666871</v>
       </c>
       <c r="M5" t="n">
-        <v>4.050161537912577</v>
+        <v>4.047897349478037</v>
       </c>
       <c r="N5" t="n">
-        <v>25.08631181999239</v>
+        <v>25.04934442507309</v>
       </c>
       <c r="O5" t="n">
-        <v>5.008623745101282</v>
+        <v>5.004932010035011</v>
       </c>
       <c r="P5" t="n">
-        <v>336.7415406238192</v>
+        <v>336.7941031205362</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21303,28 +21425,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02984120280345209</v>
+        <v>0.02277251668641368</v>
       </c>
       <c r="J6" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K6" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001787402194285304</v>
+        <v>0.00104639814706442</v>
       </c>
       <c r="M6" t="n">
-        <v>4.27719641663653</v>
+        <v>4.288303133567053</v>
       </c>
       <c r="N6" t="n">
-        <v>27.31807074879112</v>
+        <v>27.37837896980128</v>
       </c>
       <c r="O6" t="n">
-        <v>5.226669183025756</v>
+        <v>5.232435280995006</v>
       </c>
       <c r="P6" t="n">
-        <v>345.2311204562924</v>
+        <v>345.3045615097087</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21381,28 +21503,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07734901089118723</v>
+        <v>0.07019653961577986</v>
       </c>
       <c r="J7" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K7" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01347402607793591</v>
+        <v>0.01116299281097488</v>
       </c>
       <c r="M7" t="n">
-        <v>3.901163338752208</v>
+        <v>3.91248398985048</v>
       </c>
       <c r="N7" t="n">
-        <v>24.06230829691897</v>
+        <v>24.13863965937008</v>
       </c>
       <c r="O7" t="n">
-        <v>4.905334677360861</v>
+        <v>4.913108960665342</v>
       </c>
       <c r="P7" t="n">
-        <v>348.8763323690627</v>
+        <v>348.9506500048743</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21459,28 +21581,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07517741727233697</v>
+        <v>0.06565332761127313</v>
       </c>
       <c r="J8" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K8" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009160782117588862</v>
+        <v>0.007008581051736962</v>
       </c>
       <c r="M8" t="n">
-        <v>4.69288096550608</v>
+        <v>4.706965047443499</v>
       </c>
       <c r="N8" t="n">
-        <v>33.57855894665263</v>
+        <v>33.77273240328682</v>
       </c>
       <c r="O8" t="n">
-        <v>5.794700936774273</v>
+        <v>5.811431183734935</v>
       </c>
       <c r="P8" t="n">
-        <v>350.3483550393983</v>
+        <v>350.4473114103257</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21537,28 +21659,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0872096204773796</v>
+        <v>0.07603503024515416</v>
       </c>
       <c r="J9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K9" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00945754276824573</v>
+        <v>0.00720492074681145</v>
       </c>
       <c r="M9" t="n">
-        <v>5.33639043576191</v>
+        <v>5.352685969953513</v>
       </c>
       <c r="N9" t="n">
-        <v>43.75625974414547</v>
+        <v>44.05499654792425</v>
       </c>
       <c r="O9" t="n">
-        <v>6.614851452916041</v>
+        <v>6.637393806903749</v>
       </c>
       <c r="P9" t="n">
-        <v>348.879428543952</v>
+        <v>348.9955282294909</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21615,28 +21737,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1310601647374583</v>
+        <v>0.1228695080989595</v>
       </c>
       <c r="J10" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K10" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02003215046597029</v>
+        <v>0.01775639076910607</v>
       </c>
       <c r="M10" t="n">
-        <v>5.475197989568082</v>
+        <v>5.484443491496925</v>
       </c>
       <c r="N10" t="n">
-        <v>46.15750128518744</v>
+        <v>46.18384367926014</v>
       </c>
       <c r="O10" t="n">
-        <v>6.793931209924593</v>
+        <v>6.795869604344991</v>
       </c>
       <c r="P10" t="n">
-        <v>339.8206278885301</v>
+        <v>339.9057250154311</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21693,28 +21815,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1230184908359769</v>
+        <v>0.1113024633684153</v>
       </c>
       <c r="J11" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K11" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0132556572834005</v>
+        <v>0.01090802003631997</v>
       </c>
       <c r="M11" t="n">
-        <v>6.44814051486792</v>
+        <v>6.465087639816342</v>
       </c>
       <c r="N11" t="n">
-        <v>61.88149325997485</v>
+        <v>62.1208834802914</v>
       </c>
       <c r="O11" t="n">
-        <v>7.866479089146227</v>
+        <v>7.881680244737883</v>
       </c>
       <c r="P11" t="n">
-        <v>335.3481735302307</v>
+        <v>335.4699001766112</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21771,28 +21893,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1424376895847803</v>
+        <v>0.1312990757821345</v>
       </c>
       <c r="J12" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K12" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01488143145300314</v>
+        <v>0.01273742866836591</v>
       </c>
       <c r="M12" t="n">
-        <v>6.954843494577028</v>
+        <v>6.962289535897787</v>
       </c>
       <c r="N12" t="n">
-        <v>73.77517619891216</v>
+        <v>73.89440616191493</v>
       </c>
       <c r="O12" t="n">
-        <v>8.5892477085547</v>
+        <v>8.596185558834508</v>
       </c>
       <c r="P12" t="n">
-        <v>334.5116549484135</v>
+        <v>334.6273797641337</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21849,28 +21971,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1858559114889652</v>
+        <v>0.1747419840136067</v>
       </c>
       <c r="J13" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K13" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03058150340353627</v>
+        <v>0.0272270685787418</v>
       </c>
       <c r="M13" t="n">
-        <v>6.329694259215037</v>
+        <v>6.353468824060478</v>
       </c>
       <c r="N13" t="n">
-        <v>60.14809067742504</v>
+        <v>60.3312653963984</v>
       </c>
       <c r="O13" t="n">
-        <v>7.755520013346947</v>
+        <v>7.767320348511345</v>
       </c>
       <c r="P13" t="n">
-        <v>338.0571538812664</v>
+        <v>338.1726266267004</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -21927,28 +22049,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1734376012852304</v>
+        <v>0.1522664582449551</v>
       </c>
       <c r="J14" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K14" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02564960221954926</v>
+        <v>0.01952983432192279</v>
       </c>
       <c r="M14" t="n">
-        <v>6.509994147966034</v>
+        <v>6.596350921967788</v>
       </c>
       <c r="N14" t="n">
-        <v>62.76790978930122</v>
+        <v>64.36972205269643</v>
       </c>
       <c r="O14" t="n">
-        <v>7.922620134103441</v>
+        <v>8.023074351686915</v>
       </c>
       <c r="P14" t="n">
-        <v>335.1421475571463</v>
+        <v>335.3621133043484</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -21986,7 +22108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O332"/>
+  <dimension ref="A1:O334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47553,6 +47675,160 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:06:16+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-36.69364191362673,175.60403764930678</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>-36.69435828017368,175.60420708460214</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>-36.69506877757661,175.604511602208</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>-36.69575869706362,175.60487351450777</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>-36.69639654969021,175.60531661514327</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>-36.696997712594374,175.60583585081915</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>-36.69760788303428,175.60633481009407</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>-36.69820942362639,175.6068672728647</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>-36.698747914991245,175.6074939153842</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>-36.699298464854124,175.60808970151535</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>-36.69978926080776,175.60876602752512</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-36.70022592926366,175.60953757658822</t>
+        </is>
+      </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>-36.700664912345516,175.61031113214625</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>-36.69363956878371,175.6040557630706</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>-36.69435567686758,175.60422400636347</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>-36.69506093569153,175.60453983948986</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>-36.69575259345812,175.60488848587926</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>-36.696385591994655,175.60534027845063</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>-36.696995384201685,175.6058402424452</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>-36.69759818204056,175.60635080657553</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>-36.69818519996713,175.60689933778974</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>-36.698727387227926,175.60751726480768</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>-36.69927440751886,175.60811637702483</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>-36.69975960493823,175.6087964541112</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>-36.700204297177095,175.60955412007314</t>
+        </is>
+      </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>-36.70061958437486,175.6103376016356</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O334"/>
+  <dimension ref="A1:O335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17486,6 +17486,57 @@
         <v>324.38</v>
       </c>
       <c r="O334" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>326.97</v>
+      </c>
+      <c r="C335" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="D335" t="n">
+        <v>341.42</v>
+      </c>
+      <c r="E335" t="n">
+        <v>337.81</v>
+      </c>
+      <c r="F335" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="G335" t="n">
+        <v>345.32</v>
+      </c>
+      <c r="H335" t="n">
+        <v>346.37</v>
+      </c>
+      <c r="I335" t="n">
+        <v>345.07</v>
+      </c>
+      <c r="J335" t="n">
+        <v>339.19</v>
+      </c>
+      <c r="K335" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="L335" t="n">
+        <v>331.72</v>
+      </c>
+      <c r="M335" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="N335" t="n">
+        <v>327.21</v>
+      </c>
+      <c r="O335" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -17502,7 +17553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B344"/>
+  <dimension ref="A1:B345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20945,6 +20996,16 @@
       </c>
       <c r="B344" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -21113,28 +21174,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05530324827680271</v>
+        <v>0.05183786876602891</v>
       </c>
       <c r="J2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003923348125748127</v>
+        <v>0.003462280204547863</v>
       </c>
       <c r="M2" t="n">
-        <v>5.371770330185006</v>
+        <v>5.373186469338021</v>
       </c>
       <c r="N2" t="n">
-        <v>42.9412333105921</v>
+        <v>42.91690297449683</v>
       </c>
       <c r="O2" t="n">
-        <v>6.552956074215063</v>
+        <v>6.551099371441165</v>
       </c>
       <c r="P2" t="n">
-        <v>331.4425141359429</v>
+        <v>331.4786832406788</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21191,28 +21252,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07463484646708911</v>
+        <v>0.07387294971447453</v>
       </c>
       <c r="J3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01057385099178598</v>
+        <v>0.0104250331795942</v>
       </c>
       <c r="M3" t="n">
-        <v>4.212109532743692</v>
+        <v>4.202641322937876</v>
       </c>
       <c r="N3" t="n">
-        <v>28.82509869764321</v>
+        <v>28.74383460060352</v>
       </c>
       <c r="O3" t="n">
-        <v>5.368901069832002</v>
+        <v>5.361327690097251</v>
       </c>
       <c r="P3" t="n">
-        <v>328.9115264512066</v>
+        <v>328.9194785740138</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21269,28 +21330,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1303560273247323</v>
+        <v>0.1289003446510323</v>
       </c>
       <c r="J4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K4" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03642528616902241</v>
+        <v>0.03583919791267798</v>
       </c>
       <c r="M4" t="n">
-        <v>3.974626030012717</v>
+        <v>3.969999715454338</v>
       </c>
       <c r="N4" t="n">
-        <v>24.858903763918</v>
+        <v>24.80286882137662</v>
       </c>
       <c r="O4" t="n">
-        <v>4.985870411865715</v>
+        <v>4.980247867463689</v>
       </c>
       <c r="P4" t="n">
-        <v>340.4737237759194</v>
+        <v>340.4889171303337</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21347,28 +21408,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1621458537228388</v>
+        <v>0.1602368961595403</v>
       </c>
       <c r="J5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K5" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05485916296666871</v>
+        <v>0.05390376515325424</v>
       </c>
       <c r="M5" t="n">
-        <v>4.047897349478037</v>
+        <v>4.044105741436458</v>
       </c>
       <c r="N5" t="n">
-        <v>25.04934442507309</v>
+        <v>25.0059771488139</v>
       </c>
       <c r="O5" t="n">
-        <v>5.004932010035011</v>
+        <v>5.000597679159353</v>
       </c>
       <c r="P5" t="n">
-        <v>336.7941031205362</v>
+        <v>336.8140274277669</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21425,28 +21486,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02277251668641368</v>
+        <v>0.02031523972446909</v>
       </c>
       <c r="J6" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K6" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00104639814706442</v>
+        <v>0.0008366511039513691</v>
       </c>
       <c r="M6" t="n">
-        <v>4.288303133567053</v>
+        <v>4.288246180831108</v>
       </c>
       <c r="N6" t="n">
-        <v>27.37837896980128</v>
+        <v>27.34881912087503</v>
       </c>
       <c r="O6" t="n">
-        <v>5.232435280995006</v>
+        <v>5.229609844039518</v>
       </c>
       <c r="P6" t="n">
-        <v>345.3045615097087</v>
+        <v>345.3302087750445</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21503,28 +21564,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07019653961577986</v>
+        <v>0.06699233662966762</v>
       </c>
       <c r="J7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01116299281097488</v>
+        <v>0.0102042863147388</v>
       </c>
       <c r="M7" t="n">
-        <v>3.91248398985048</v>
+        <v>3.916156281881208</v>
       </c>
       <c r="N7" t="n">
-        <v>24.13863965937008</v>
+        <v>24.15548458040977</v>
       </c>
       <c r="O7" t="n">
-        <v>4.913108960665342</v>
+        <v>4.91482294497063</v>
       </c>
       <c r="P7" t="n">
-        <v>348.9506500048743</v>
+        <v>348.9840931394688</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21581,28 +21642,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06565332761127313</v>
+        <v>0.0622581160445996</v>
       </c>
       <c r="J8" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K8" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007008581051736962</v>
+        <v>0.006328267998341852</v>
       </c>
       <c r="M8" t="n">
-        <v>4.706965047443499</v>
+        <v>4.708103480920776</v>
       </c>
       <c r="N8" t="n">
-        <v>33.77273240328682</v>
+        <v>33.77167419784823</v>
       </c>
       <c r="O8" t="n">
-        <v>5.811431183734935</v>
+        <v>5.811340137855315</v>
       </c>
       <c r="P8" t="n">
-        <v>350.4473114103257</v>
+        <v>350.4827481532205</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21659,28 +21720,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07603503024515416</v>
+        <v>0.07256720399930162</v>
       </c>
       <c r="J9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00720492074681145</v>
+        <v>0.006593055390535119</v>
       </c>
       <c r="M9" t="n">
-        <v>5.352685969953513</v>
+        <v>5.351477318611848</v>
       </c>
       <c r="N9" t="n">
-        <v>44.05499654792425</v>
+        <v>44.02747883553504</v>
       </c>
       <c r="O9" t="n">
-        <v>6.637393806903749</v>
+        <v>6.635320552583352</v>
       </c>
       <c r="P9" t="n">
-        <v>348.9955282294909</v>
+        <v>349.0317228714638</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21737,28 +21798,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1228695080989595</v>
+        <v>0.1205566121254509</v>
       </c>
       <c r="J10" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K10" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01775639076910607</v>
+        <v>0.0171959434398935</v>
       </c>
       <c r="M10" t="n">
-        <v>5.484443491496925</v>
+        <v>5.479775605622495</v>
       </c>
       <c r="N10" t="n">
-        <v>46.18384367926014</v>
+        <v>46.09200197060621</v>
       </c>
       <c r="O10" t="n">
-        <v>6.795869604344991</v>
+        <v>6.789109070460293</v>
       </c>
       <c r="P10" t="n">
-        <v>339.9057250154311</v>
+        <v>339.9298653372774</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21815,28 +21876,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1113024633684153</v>
+        <v>0.1072938079254259</v>
       </c>
       <c r="J11" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K11" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01090802003631997</v>
+        <v>0.01018575535298782</v>
       </c>
       <c r="M11" t="n">
-        <v>6.465087639816342</v>
+        <v>6.464803442544821</v>
       </c>
       <c r="N11" t="n">
-        <v>62.1208834802914</v>
+        <v>62.0743736496918</v>
       </c>
       <c r="O11" t="n">
-        <v>7.881680244737883</v>
+        <v>7.87872919002118</v>
       </c>
       <c r="P11" t="n">
-        <v>335.4699001766112</v>
+        <v>335.511739599427</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21893,28 +21954,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1312990757821345</v>
+        <v>0.1275737898628455</v>
       </c>
       <c r="J12" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K12" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01273742866836591</v>
+        <v>0.01208993752212617</v>
       </c>
       <c r="M12" t="n">
-        <v>6.962289535897787</v>
+        <v>6.957960308756795</v>
       </c>
       <c r="N12" t="n">
-        <v>73.89440616191493</v>
+        <v>73.79362360947741</v>
       </c>
       <c r="O12" t="n">
-        <v>8.596185558834508</v>
+        <v>8.590321507922589</v>
       </c>
       <c r="P12" t="n">
-        <v>334.6273797641337</v>
+        <v>334.6662615824648</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -21971,28 +22032,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1747419840136067</v>
+        <v>0.1706746314241951</v>
       </c>
       <c r="J13" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K13" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0272270685787418</v>
+        <v>0.02610811532619517</v>
       </c>
       <c r="M13" t="n">
-        <v>6.353468824060478</v>
+        <v>6.357656732023313</v>
       </c>
       <c r="N13" t="n">
-        <v>60.3312653963984</v>
+        <v>60.29422833409924</v>
       </c>
       <c r="O13" t="n">
-        <v>7.767320348511345</v>
+        <v>7.764935822922122</v>
       </c>
       <c r="P13" t="n">
-        <v>338.1726266267004</v>
+        <v>338.2150786875345</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22049,28 +22110,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1522664582449551</v>
+        <v>0.145150813860268</v>
       </c>
       <c r="J14" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K14" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01952983432192279</v>
+        <v>0.01777096289633928</v>
       </c>
       <c r="M14" t="n">
-        <v>6.596350921967788</v>
+        <v>6.618277541118996</v>
       </c>
       <c r="N14" t="n">
-        <v>64.36972205269643</v>
+        <v>64.61648485785247</v>
       </c>
       <c r="O14" t="n">
-        <v>8.023074351686915</v>
+        <v>8.038437961311418</v>
       </c>
       <c r="P14" t="n">
-        <v>335.3621133043484</v>
+        <v>335.4363812124416</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22108,7 +22169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O334"/>
+  <dimension ref="A1:O335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47829,6 +47890,83 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-36.69363756708632,175.60407122603868</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>-36.694354966874606,175.60422862138907</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>-36.69505987835823,175.60454364676335</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>-36.69575157619037,175.6048909811076</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>-36.696383301656084,175.60534522446892</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>-36.696993947533755,175.60584295217174</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>-36.697591190820376,175.60636233476353</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>-36.69817601593136,175.6069114947153</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-36.69871821948762,175.60752769270155</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-36.699266343606396,175.6081253185327</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-36.69975370154417,175.60880251092297</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>-36.70019677964298,175.60955986922536</t>
+        </is>
+      </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>-36.700596512762,175.61035107440375</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O335"/>
+  <dimension ref="A1:O338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17539,6 +17539,159 @@
       <c r="O335" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>325.53</v>
+      </c>
+      <c r="C336" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="D336" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="E336" t="n">
+        <v>337.78</v>
+      </c>
+      <c r="F336" t="n">
+        <v>340.87</v>
+      </c>
+      <c r="G336" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="H336" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="I336" t="n">
+        <v>343.31</v>
+      </c>
+      <c r="J336" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="K336" t="n">
+        <v>330.66</v>
+      </c>
+      <c r="L336" t="n">
+        <v>331.04</v>
+      </c>
+      <c r="M336" t="n">
+        <v>335.68</v>
+      </c>
+      <c r="N336" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>325.22</v>
+      </c>
+      <c r="C337" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D337" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="E337" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="F337" t="n">
+        <v>342.03</v>
+      </c>
+      <c r="G337" t="n">
+        <v>345.54</v>
+      </c>
+      <c r="H337" t="n">
+        <v>345.81</v>
+      </c>
+      <c r="I337" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="J337" t="n">
+        <v>338.15</v>
+      </c>
+      <c r="K337" t="n">
+        <v>333.41</v>
+      </c>
+      <c r="L337" t="n">
+        <v>330.56</v>
+      </c>
+      <c r="M337" t="n">
+        <v>336.68</v>
+      </c>
+      <c r="N337" t="n">
+        <v>329.18</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="C338" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="D338" t="n">
+        <v>340.38</v>
+      </c>
+      <c r="E338" t="n">
+        <v>339.05</v>
+      </c>
+      <c r="F338" t="n">
+        <v>341.67</v>
+      </c>
+      <c r="G338" t="n">
+        <v>345.45</v>
+      </c>
+      <c r="H338" t="n">
+        <v>346.05</v>
+      </c>
+      <c r="I338" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="J338" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="K338" t="n">
+        <v>333.42</v>
+      </c>
+      <c r="L338" t="n">
+        <v>330.75</v>
+      </c>
+      <c r="M338" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="N338" t="n">
+        <v>330.33</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21006,6 +21159,36 @@
       </c>
       <c r="B345" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -21174,28 +21357,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05183786876602891</v>
+        <v>0.03926306081954158</v>
       </c>
       <c r="J2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003462280204547863</v>
+        <v>0.002006208945889876</v>
       </c>
       <c r="M2" t="n">
-        <v>5.373186469338021</v>
+        <v>5.389947710064168</v>
       </c>
       <c r="N2" t="n">
-        <v>42.91690297449683</v>
+        <v>42.99239433817131</v>
       </c>
       <c r="O2" t="n">
-        <v>6.551099371441165</v>
+        <v>6.556858572378339</v>
       </c>
       <c r="P2" t="n">
-        <v>331.4786832406788</v>
+        <v>331.6109095744842</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21252,28 +21435,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07387294971447453</v>
+        <v>0.07173767220594372</v>
       </c>
       <c r="J3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0104250331795942</v>
+        <v>0.01002117725077767</v>
       </c>
       <c r="M3" t="n">
-        <v>4.202641322937876</v>
+        <v>4.173799121189888</v>
       </c>
       <c r="N3" t="n">
-        <v>28.74383460060352</v>
+        <v>28.50187108995394</v>
       </c>
       <c r="O3" t="n">
-        <v>5.361327690097251</v>
+        <v>5.338714366769769</v>
       </c>
       <c r="P3" t="n">
-        <v>328.9194785740138</v>
+        <v>328.9419262547484</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21330,28 +21513,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1289003446510323</v>
+        <v>0.1228929160850482</v>
       </c>
       <c r="J4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03583919791267798</v>
+        <v>0.03316072068722953</v>
       </c>
       <c r="M4" t="n">
-        <v>3.969999715454338</v>
+        <v>3.964044978380704</v>
       </c>
       <c r="N4" t="n">
-        <v>24.80286882137662</v>
+        <v>24.68628138067595</v>
       </c>
       <c r="O4" t="n">
-        <v>4.980247867463689</v>
+        <v>4.96852909628956</v>
       </c>
       <c r="P4" t="n">
-        <v>340.4889171303337</v>
+        <v>340.5520886944103</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21408,28 +21591,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1602368961595403</v>
+        <v>0.155885086734201</v>
       </c>
       <c r="J5" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05390376515325424</v>
+        <v>0.05199095643049223</v>
       </c>
       <c r="M5" t="n">
-        <v>4.044105741436458</v>
+        <v>4.026815238477891</v>
       </c>
       <c r="N5" t="n">
-        <v>25.0059771488139</v>
+        <v>24.84079333733462</v>
       </c>
       <c r="O5" t="n">
-        <v>5.000597679159353</v>
+        <v>4.984053905941891</v>
       </c>
       <c r="P5" t="n">
-        <v>336.8140274277669</v>
+        <v>336.8597765910645</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21486,28 +21669,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02031523972446909</v>
+        <v>0.01279226948802264</v>
       </c>
       <c r="J6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008366511039513691</v>
+        <v>0.0003362952012112563</v>
       </c>
       <c r="M6" t="n">
-        <v>4.288246180831108</v>
+        <v>4.288247924366209</v>
       </c>
       <c r="N6" t="n">
-        <v>27.34881912087503</v>
+        <v>27.27093977244362</v>
       </c>
       <c r="O6" t="n">
-        <v>5.229609844039518</v>
+        <v>5.222158535743971</v>
       </c>
       <c r="P6" t="n">
-        <v>345.3302087750445</v>
+        <v>345.4093074506886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21564,28 +21747,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06699233662966762</v>
+        <v>0.05766854530831995</v>
       </c>
       <c r="J7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0102042863147388</v>
+        <v>0.007648019136628825</v>
       </c>
       <c r="M7" t="n">
-        <v>3.916156281881208</v>
+        <v>3.925696949307468</v>
       </c>
       <c r="N7" t="n">
-        <v>24.15548458040977</v>
+        <v>24.19170167339011</v>
       </c>
       <c r="O7" t="n">
-        <v>4.91482294497063</v>
+        <v>4.918506040800408</v>
       </c>
       <c r="P7" t="n">
-        <v>348.9840931394688</v>
+        <v>349.082133889959</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21642,28 +21825,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0622581160445996</v>
+        <v>0.05123602056502204</v>
       </c>
       <c r="J8" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006328267998341852</v>
+        <v>0.004332437449979909</v>
       </c>
       <c r="M8" t="n">
-        <v>4.708103480920776</v>
+        <v>4.714445339278189</v>
       </c>
       <c r="N8" t="n">
-        <v>33.77167419784823</v>
+        <v>33.8224053671757</v>
       </c>
       <c r="O8" t="n">
-        <v>5.811340137855315</v>
+        <v>5.815703342432084</v>
       </c>
       <c r="P8" t="n">
-        <v>350.4827481532205</v>
+        <v>350.5986448188489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21720,28 +21903,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07256720399930162</v>
+        <v>0.06115570549598398</v>
       </c>
       <c r="J9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006593055390535119</v>
+        <v>0.00474090544782324</v>
       </c>
       <c r="M9" t="n">
-        <v>5.351477318611848</v>
+        <v>5.351576297787929</v>
       </c>
       <c r="N9" t="n">
-        <v>44.02747883553504</v>
+        <v>44.01700332030966</v>
       </c>
       <c r="O9" t="n">
-        <v>6.635320552583352</v>
+        <v>6.634531130404745</v>
       </c>
       <c r="P9" t="n">
-        <v>349.0317228714638</v>
+        <v>349.1517027176798</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21798,28 +21981,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1205566121254509</v>
+        <v>0.1120537100649131</v>
       </c>
       <c r="J10" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K10" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0171959434398935</v>
+        <v>0.01510742693364642</v>
       </c>
       <c r="M10" t="n">
-        <v>5.479775605622495</v>
+        <v>5.473837567360461</v>
       </c>
       <c r="N10" t="n">
-        <v>46.09200197060621</v>
+        <v>45.89046848286485</v>
       </c>
       <c r="O10" t="n">
-        <v>6.789109070460293</v>
+        <v>6.774250400071202</v>
       </c>
       <c r="P10" t="n">
-        <v>339.9298653372774</v>
+        <v>340.0192763613351</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21876,28 +22059,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1072938079254259</v>
+        <v>0.09714340725870832</v>
       </c>
       <c r="J11" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K11" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01018575535298782</v>
+        <v>0.008483351999989175</v>
       </c>
       <c r="M11" t="n">
-        <v>6.464803442544821</v>
+        <v>6.454416121554909</v>
       </c>
       <c r="N11" t="n">
-        <v>62.0743736496918</v>
+        <v>61.83449774041019</v>
       </c>
       <c r="O11" t="n">
-        <v>7.87872919002118</v>
+        <v>7.863491447214157</v>
       </c>
       <c r="P11" t="n">
-        <v>335.511739599427</v>
+        <v>335.6184482294397</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21954,28 +22137,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1275737898628455</v>
+        <v>0.114985485465242</v>
       </c>
       <c r="J12" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K12" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01208993752212617</v>
+        <v>0.009971488134068118</v>
       </c>
       <c r="M12" t="n">
-        <v>6.957960308756795</v>
+        <v>6.950707324055909</v>
       </c>
       <c r="N12" t="n">
-        <v>73.79362360947741</v>
+        <v>73.59451064351565</v>
       </c>
       <c r="O12" t="n">
-        <v>8.590321507922589</v>
+        <v>8.578724301638074</v>
       </c>
       <c r="P12" t="n">
-        <v>334.6662615824648</v>
+        <v>334.7986365381983</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22032,28 +22215,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1706746314241951</v>
+        <v>0.1594222538319956</v>
       </c>
       <c r="J13" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K13" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02610811532619517</v>
+        <v>0.02314967979195348</v>
       </c>
       <c r="M13" t="n">
-        <v>6.357656732023313</v>
+        <v>6.364120553576836</v>
       </c>
       <c r="N13" t="n">
-        <v>60.29422833409924</v>
+        <v>60.12465185918646</v>
       </c>
       <c r="O13" t="n">
-        <v>7.764935822922122</v>
+        <v>7.754008760582261</v>
       </c>
       <c r="P13" t="n">
-        <v>338.2150786875345</v>
+        <v>338.3333950277898</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22110,28 +22293,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.145150813860268</v>
+        <v>0.127419629268969</v>
       </c>
       <c r="J14" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K14" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01777096289633928</v>
+        <v>0.01381827385766987</v>
       </c>
       <c r="M14" t="n">
-        <v>6.618277541118996</v>
+        <v>6.661513838881646</v>
       </c>
       <c r="N14" t="n">
-        <v>64.61648485785247</v>
+        <v>64.96021894143863</v>
       </c>
       <c r="O14" t="n">
-        <v>8.038437961311418</v>
+        <v>8.059790254183953</v>
       </c>
       <c r="P14" t="n">
-        <v>335.4363812124416</v>
+        <v>335.6228081056534</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22169,7 +22352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O335"/>
+  <dimension ref="A1:O338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47967,6 +48150,237 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-36.69363962597504,175.6040553212715</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-36.69435554163084,175.60422488541596</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-36.6950626685431,175.6045335997914</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-36.69575169826249,175.6048906816802</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-36.696387029069726,175.60533717506647</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-36.6969947897184,175.60584136371133</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-36.69759623100248,175.6063540237445</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>-36.69818686418823,175.6068971348566</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-36.698724796344884,175.60752021182142</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-36.69927232434153,175.60811868691457</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>-36.69975842425944,175.60879766547362</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>-36.700197930285974,175.60955898925317</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>-36.700593007181126,175.61035312150213</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-36.69364006920775,175.60405189732842</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-36.69435442592746,175.60423213759898</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-36.69506260980238,175.6045338113066</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-36.69574738504667,175.60490126144762</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-36.6963818196722,175.60534842483355</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-36.696992857647714,175.6058450078263</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-36.69759422576879,175.60635733027905</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>-36.69817866635791,175.6069079863411</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>-36.69872512850937,175.60751983399916</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-36.69925384454086,175.6081391778662</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>-36.699761757940706,175.60879424515608</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>-36.70019025933261,175.60956485573405</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>-36.700580452309865,175.61036045296927</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-36.693638911083355,175.6040608437602</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-36.69435459497345,175.60423103878338</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-36.69506293287637,175.60453264797295</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-36.69574653054155,175.60490335743916</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-36.69638343638188,175.6053449335267</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-36.69699330351018,175.60584416687672</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-36.69759292507665,175.60635947505818</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>-36.69817552282875,175.60691214743605</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>-36.698724065583,175.60752104303037</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-36.69925377734158,175.60813925237872</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>-36.699760438358545,175.6087955990318</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>-36.700192560618646,175.6095630957899</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>-36.70057107691874,175.61036592776466</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0152/nzd0152.xlsx
+++ b/data/nzd0152/nzd0152.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O338"/>
+  <dimension ref="A1:O340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17690,6 +17690,108 @@
         <v>330.33</v>
       </c>
       <c r="O338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="C339" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="D339" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="E339" t="n">
+        <v>337.42</v>
+      </c>
+      <c r="F339" t="n">
+        <v>339.82</v>
+      </c>
+      <c r="G339" t="n">
+        <v>343.32</v>
+      </c>
+      <c r="H339" t="n">
+        <v>342.81</v>
+      </c>
+      <c r="I339" t="n">
+        <v>345.15</v>
+      </c>
+      <c r="J339" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="K339" t="n">
+        <v>330.26</v>
+      </c>
+      <c r="L339" t="n">
+        <v>326.94</v>
+      </c>
+      <c r="M339" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="N339" t="n">
+        <v>326.65</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>326.15</v>
+      </c>
+      <c r="C340" t="n">
+        <v>327.2</v>
+      </c>
+      <c r="D340" t="n">
+        <v>337.89</v>
+      </c>
+      <c r="E340" t="n">
+        <v>337.29</v>
+      </c>
+      <c r="F340" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="G340" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="H340" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="I340" t="n">
+        <v>345.11</v>
+      </c>
+      <c r="J340" t="n">
+        <v>334.04</v>
+      </c>
+      <c r="K340" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="L340" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="M340" t="n">
+        <v>333.23</v>
+      </c>
+      <c r="N340" t="n">
+        <v>326.77</v>
+      </c>
+      <c r="O340" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17706,7 +17808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21189,6 +21291,26 @@
       </c>
       <c r="B348" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -21357,28 +21479,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03926306081954158</v>
+        <v>0.03178028165975938</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002006208945889876</v>
+        <v>0.001324191963844368</v>
       </c>
       <c r="M2" t="n">
-        <v>5.389947710064168</v>
+        <v>5.397688422082291</v>
       </c>
       <c r="N2" t="n">
-        <v>42.99239433817131</v>
+        <v>42.98849384304788</v>
       </c>
       <c r="O2" t="n">
-        <v>6.556858572378339</v>
+        <v>6.556561129361023</v>
       </c>
       <c r="P2" t="n">
-        <v>331.6109095744842</v>
+        <v>331.6898116808533</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21435,28 +21557,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07173767220594372</v>
+        <v>0.06764514366519009</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01002117725077767</v>
+        <v>0.009008634935286364</v>
       </c>
       <c r="M3" t="n">
-        <v>4.173799121189888</v>
+        <v>4.1653751244334</v>
       </c>
       <c r="N3" t="n">
-        <v>28.50187108995394</v>
+        <v>28.4084339299686</v>
       </c>
       <c r="O3" t="n">
-        <v>5.338714366769769</v>
+        <v>5.329956278429364</v>
       </c>
       <c r="P3" t="n">
-        <v>328.9419262547484</v>
+        <v>328.985080448721</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21513,28 +21635,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1228929160850482</v>
+        <v>0.1161085118539992</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03316072068722953</v>
+        <v>0.02982881635611867</v>
       </c>
       <c r="M4" t="n">
-        <v>3.964044978380704</v>
+        <v>3.973944438827752</v>
       </c>
       <c r="N4" t="n">
-        <v>24.68628138067595</v>
+        <v>24.74592155934883</v>
       </c>
       <c r="O4" t="n">
-        <v>4.96852909628956</v>
+        <v>4.974527269937198</v>
       </c>
       <c r="P4" t="n">
-        <v>340.5520886944103</v>
+        <v>340.6236269914633</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21591,28 +21713,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.155885086734201</v>
+        <v>0.1517204944040896</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05199095643049223</v>
+        <v>0.04983085328145032</v>
       </c>
       <c r="M5" t="n">
-        <v>4.026815238477891</v>
+        <v>4.020750219530814</v>
       </c>
       <c r="N5" t="n">
-        <v>24.84079333733462</v>
+        <v>24.77161163281284</v>
       </c>
       <c r="O5" t="n">
-        <v>4.984053905941891</v>
+        <v>4.977108762405423</v>
       </c>
       <c r="P5" t="n">
-        <v>336.8597765910645</v>
+        <v>336.9036906857561</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -21669,28 +21791,28 @@
         <v>0.1704</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01279226948802264</v>
+        <v>0.005834506323085473</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0003362952012112563</v>
+        <v>7.030122244433556e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>4.288247924366209</v>
+        <v>4.298171081192312</v>
       </c>
       <c r="N6" t="n">
-        <v>27.27093977244362</v>
+        <v>27.32612081231033</v>
       </c>
       <c r="O6" t="n">
-        <v>5.222158535743971</v>
+        <v>5.227439221292805</v>
       </c>
       <c r="P6" t="n">
-        <v>345.4093074506886</v>
+        <v>345.4826749143849</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -21747,28 +21869,28 @@
         <v>0.1918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05766854530831995</v>
+        <v>0.04927109125179817</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007648019136628825</v>
+        <v>0.005592067926170508</v>
       </c>
       <c r="M7" t="n">
-        <v>3.925696949307468</v>
+        <v>3.943226910117837</v>
       </c>
       <c r="N7" t="n">
-        <v>24.19170167339011</v>
+        <v>24.36349941952754</v>
       </c>
       <c r="O7" t="n">
-        <v>4.918506040800408</v>
+        <v>4.935939568058703</v>
       </c>
       <c r="P7" t="n">
-        <v>349.082133889959</v>
+        <v>349.1706816421606</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21825,28 +21947,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05123602056502204</v>
+        <v>0.04088882892909437</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004332437449979909</v>
+        <v>0.002759390137484496</v>
       </c>
       <c r="M8" t="n">
-        <v>4.714445339278189</v>
+        <v>4.731751149501934</v>
       </c>
       <c r="N8" t="n">
-        <v>33.8224053671757</v>
+        <v>34.10039082368623</v>
       </c>
       <c r="O8" t="n">
-        <v>5.815703342432084</v>
+        <v>5.839553991846143</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5986448188489</v>
+        <v>350.7077507753399</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21903,28 +22025,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06115570549598398</v>
+        <v>0.05471556664034791</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00474090544782324</v>
+        <v>0.00383032479639589</v>
       </c>
       <c r="M9" t="n">
-        <v>5.351576297787929</v>
+        <v>5.347128465552373</v>
       </c>
       <c r="N9" t="n">
-        <v>44.01700332030966</v>
+        <v>43.94228952638224</v>
       </c>
       <c r="O9" t="n">
-        <v>6.634531130404745</v>
+        <v>6.628898062753887</v>
       </c>
       <c r="P9" t="n">
-        <v>349.1517027176798</v>
+        <v>349.2196111351453</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21981,28 +22103,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1120537100649131</v>
+        <v>0.1017520486290474</v>
       </c>
       <c r="J10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K10" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01510742693364642</v>
+        <v>0.01251823115222883</v>
       </c>
       <c r="M10" t="n">
-        <v>5.473837567360461</v>
+        <v>5.493615379166401</v>
       </c>
       <c r="N10" t="n">
-        <v>45.89046848286485</v>
+        <v>46.09306704884158</v>
       </c>
       <c r="O10" t="n">
-        <v>6.774250400071202</v>
+        <v>6.789187510213692</v>
       </c>
       <c r="P10" t="n">
-        <v>340.0192763613351</v>
+        <v>340.127902198702</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22059,28 +22181,28 @@
         <v>0.1989</v>
       </c>
       <c r="I11" t="n">
-        <v>0.09714340725870832</v>
+        <v>0.087905626384136</v>
       </c>
       <c r="J11" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K11" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008483351999989175</v>
+        <v>0.007001681402518334</v>
       </c>
       <c r="M11" t="n">
-        <v>6.454416121554909</v>
+        <v>6.458717626678385</v>
       </c>
       <c r="N11" t="n">
-        <v>61.83449774041019</v>
+        <v>61.85042348287269</v>
       </c>
       <c r="O11" t="n">
-        <v>7.863491447214157</v>
+        <v>7.864504020144734</v>
       </c>
       <c r="P11" t="n">
-        <v>335.6184482294397</v>
+        <v>335.7158573716239</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22137,28 +22259,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.114985485465242</v>
+        <v>0.1027648284537485</v>
       </c>
       <c r="J12" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K12" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L12" t="n">
-        <v>0.009971488134068118</v>
+        <v>0.008008426690882642</v>
       </c>
       <c r="M12" t="n">
-        <v>6.950707324055909</v>
+        <v>6.963201244173126</v>
       </c>
       <c r="N12" t="n">
-        <v>73.59451064351565</v>
+        <v>73.82661319252293</v>
       </c>
       <c r="O12" t="n">
-        <v>8.578724301638074</v>
+        <v>8.592241453341668</v>
       </c>
       <c r="P12" t="n">
-        <v>334.7986365381983</v>
+        <v>334.9274966325081</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -22215,28 +22337,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1594222538319956</v>
+        <v>0.1488647364368933</v>
       </c>
       <c r="J13" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K13" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02314967979195348</v>
+        <v>0.02033042320241474</v>
       </c>
       <c r="M13" t="n">
-        <v>6.364120553576836</v>
+        <v>6.385077402994115</v>
       </c>
       <c r="N13" t="n">
-        <v>60.12465185918646</v>
+        <v>60.26706360241457</v>
       </c>
       <c r="O13" t="n">
-        <v>7.754008760582261</v>
+        <v>7.763186433573173</v>
       </c>
       <c r="P13" t="n">
-        <v>338.3333950277898</v>
+        <v>338.44471970599</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -22293,28 +22415,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.127419629268969</v>
+        <v>0.1133965034580159</v>
       </c>
       <c r="J14" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K14" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01381827385766987</v>
+        <v>0.01096572923292027</v>
       </c>
       <c r="M14" t="n">
-        <v>6.661513838881646</v>
+        <v>6.702378560884913</v>
       </c>
       <c r="N14" t="n">
-        <v>64.96021894143863</v>
+        <v>65.45401823438975</v>
       </c>
       <c r="O14" t="n">
-        <v>8.059790254183953</v>
+        <v>8.090365766415617</v>
       </c>
       <c r="P14" t="n">
-        <v>335.6228081056534</v>
+        <v>335.7706751806921</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -22352,7 +22474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O338"/>
+  <dimension ref="A1:O340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48381,6 +48503,160 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-36.693638911083355,175.6040608437602</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-36.694358787310954,175.60420378815496</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-36.69507036357504,175.60450589129633</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-36.69575316312804,175.60488708855135</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-36.69639174447181,175.60532699208628</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-36.69700385558715,175.60582426440024</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-36.69761048441772,175.60633052053413</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>-36.69817552282875,175.60691214743605</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>-36.69875349535339,175.60748756796596</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-36.69927501231227,175.60811570641167</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>-36.69978689945072,175.6087684502518</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>-36.70021542005874,175.60954561367245</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>-36.70060107816959,175.6103484084149</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-36.693638739509325,175.6040621691575</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-36.69435899016584,175.60420246957608</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-36.695070246093685,175.60450631432684</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-36.695753692107246,175.60488579103256</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-36.696393316272314,175.60532359775928</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-36.697004598691045,175.60582286281718</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-36.69760967148542,175.60633186102163</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>-36.698175769380065,175.60691182107567</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>-36.69875243242729,175.60748877699805</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>-36.69927722988809,175.60811324749665</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>-36.699784190835246,175.60877122926163</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>-36.700216724120686,175.60954461637016</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>-36.70060009986796,175.61034897969827</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
